--- a/LoanOfficer-A/2023/122 moirangthem naobi.xlsx
+++ b/LoanOfficer-A/2023/122 moirangthem naobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1400</v>
+        <v>4600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>22600</v>
+        <v>19400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1086,6 +1086,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
+      <c r="B10" s="3">
+        <v>45844</v>
+      </c>
+      <c r="C10" s="4">
+        <v>200</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1109,9 +1118,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45844</v>
+      </c>
+      <c r="C11" s="4">
+        <v>200</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1135,9 +1150,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45844</v>
+      </c>
+      <c r="C12" s="4">
+        <v>200</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1161,9 +1182,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45844</v>
+      </c>
+      <c r="C13" s="4">
+        <v>200</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1187,9 +1214,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45844</v>
+      </c>
+      <c r="C14" s="4">
+        <v>200</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1213,9 +1246,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45844</v>
+      </c>
+      <c r="C15" s="4">
+        <v>200</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1239,9 +1278,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45851</v>
+      </c>
+      <c r="C16" s="4">
+        <v>200</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1265,9 +1310,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45851</v>
+      </c>
+      <c r="C17" s="4">
+        <v>200</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1291,9 +1342,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45851</v>
+      </c>
+      <c r="C18" s="4">
+        <v>200</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1317,9 +1374,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45851</v>
+      </c>
+      <c r="C19" s="4">
+        <v>200</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1343,9 +1406,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45851</v>
+      </c>
+      <c r="C20" s="4">
+        <v>200</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1369,9 +1438,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45851</v>
+      </c>
+      <c r="C21" s="4">
+        <v>200</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1395,9 +1470,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45851</v>
+      </c>
+      <c r="C22" s="4">
+        <v>200</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1421,9 +1502,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45851</v>
+      </c>
+      <c r="C23" s="4">
+        <v>200</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1447,9 +1534,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45851</v>
+      </c>
+      <c r="C24" s="4">
+        <v>200</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1473,9 +1566,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45851</v>
+      </c>
+      <c r="C25" s="4">
+        <v>200</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>

--- a/LoanOfficer-A/2023/122 moirangthem naobi.xlsx
+++ b/LoanOfficer-A/2023/122 moirangthem naobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4600</v>
+        <v>6600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>19400</v>
+        <v>17400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -874,9 +874,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45864</v>
+      </c>
+      <c r="G3" s="4">
+        <v>200</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -906,9 +912,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45864</v>
+      </c>
+      <c r="G4" s="4">
+        <v>200</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -938,9 +950,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45864</v>
+      </c>
+      <c r="G5" s="4">
+        <v>200</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -1598,9 +1616,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45856</v>
+      </c>
+      <c r="C26" s="4">
+        <v>200</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1624,9 +1648,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45856</v>
+      </c>
+      <c r="C27" s="4">
+        <v>200</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1650,9 +1680,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45856</v>
+      </c>
+      <c r="C28" s="4">
+        <v>200</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>
@@ -1676,9 +1712,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45864</v>
+      </c>
+      <c r="C29" s="4">
+        <v>200</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1702,9 +1744,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45864</v>
+      </c>
+      <c r="C30" s="4">
+        <v>200</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1728,9 +1776,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45864</v>
+      </c>
+      <c r="C31" s="4">
+        <v>200</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1754,9 +1808,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45864</v>
+      </c>
+      <c r="C32" s="4">
+        <v>200</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/122 moirangthem naobi.xlsx
+++ b/LoanOfficer-A/2023/122 moirangthem naobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>6600</v>
+        <v>10000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>17400</v>
+        <v>14000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -988,9 +988,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45865</v>
+      </c>
+      <c r="G6" s="4">
+        <v>200</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -1020,9 +1026,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45867</v>
+      </c>
+      <c r="G7" s="4">
+        <v>200</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1052,9 +1064,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45867</v>
+      </c>
+      <c r="G8" s="4">
+        <v>200</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1084,9 +1102,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45871</v>
+      </c>
+      <c r="G9" s="4">
+        <v>200</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1116,9 +1140,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45871</v>
+      </c>
+      <c r="G10" s="4">
+        <v>200</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1148,9 +1178,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45871</v>
+      </c>
+      <c r="G11" s="4">
+        <v>200</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1180,9 +1216,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45876</v>
+      </c>
+      <c r="G12" s="4">
+        <v>200</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1212,9 +1254,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45876</v>
+      </c>
+      <c r="G13" s="4">
+        <v>200</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1244,9 +1292,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45880</v>
+      </c>
+      <c r="G14" s="4">
+        <v>200</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -1276,9 +1330,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45880</v>
+      </c>
+      <c r="G15" s="4">
+        <v>200</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1308,9 +1368,15 @@
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>45880</v>
+      </c>
+      <c r="G16" s="4">
+        <v>200</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>
@@ -1340,9 +1406,15 @@
       <c r="E17" s="1">
         <v>45</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="3">
+        <v>45880</v>
+      </c>
+      <c r="G17" s="4">
+        <v>200</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
       <c r="I17" s="1">
         <v>75</v>
       </c>
@@ -1372,9 +1444,15 @@
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>45880</v>
+      </c>
+      <c r="G18" s="4">
+        <v>200</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>
@@ -1404,9 +1482,15 @@
       <c r="E19" s="1">
         <v>47</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="F19" s="3">
+        <v>45880</v>
+      </c>
+      <c r="G19" s="4">
+        <v>200</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
       <c r="I19" s="1">
         <v>77</v>
       </c>
@@ -1436,9 +1520,15 @@
       <c r="E20" s="1">
         <v>48</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
+      <c r="F20" s="3">
+        <v>45880</v>
+      </c>
+      <c r="G20" s="4">
+        <v>200</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
       <c r="I20" s="1">
         <v>78</v>
       </c>
@@ -1468,9 +1558,15 @@
       <c r="E21" s="1">
         <v>49</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
+      <c r="F21" s="3">
+        <v>45880</v>
+      </c>
+      <c r="G21" s="4">
+        <v>200</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
       <c r="I21" s="1">
         <v>79</v>
       </c>
@@ -1500,9 +1596,15 @@
       <c r="E22" s="1">
         <v>50</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="3">
+        <v>45880</v>
+      </c>
+      <c r="G22" s="4">
+        <v>200</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
       <c r="I22" s="1">
         <v>80</v>
       </c>

--- a/LoanOfficer-A/2023/122 moirangthem naobi.xlsx
+++ b/LoanOfficer-A/2023/122 moirangthem naobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>10000</v>
+        <v>12600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>14000</v>
+        <v>11400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -886,9 +886,15 @@
       <c r="I3" s="1">
         <v>61</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="3">
+        <v>45894</v>
+      </c>
+      <c r="K3" s="4">
+        <v>200</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
       <c r="M3" s="1">
         <v>91</v>
       </c>
@@ -924,9 +930,15 @@
       <c r="I4" s="1">
         <v>62</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1"/>
+      <c r="J4" s="3">
+        <v>45894</v>
+      </c>
+      <c r="K4" s="4">
+        <v>200</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
       <c r="M4" s="1">
         <v>92</v>
       </c>
@@ -962,9 +974,15 @@
       <c r="I5" s="1">
         <v>63</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="3">
+        <v>45894</v>
+      </c>
+      <c r="K5" s="4">
+        <v>200</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
       <c r="M5" s="1">
         <v>93</v>
       </c>
@@ -1634,9 +1652,15 @@
       <c r="E23" s="1">
         <v>51</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="3">
+        <v>45885</v>
+      </c>
+      <c r="G23" s="4">
+        <v>200</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
       <c r="I23" s="1">
         <v>81</v>
       </c>
@@ -1666,9 +1690,15 @@
       <c r="E24" s="1">
         <v>52</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
+      <c r="F24" s="3">
+        <v>45885</v>
+      </c>
+      <c r="G24" s="4">
+        <v>200</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
       <c r="I24" s="1">
         <v>82</v>
       </c>
@@ -1698,9 +1728,15 @@
       <c r="E25" s="1">
         <v>53</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="3">
+        <v>45885</v>
+      </c>
+      <c r="G25" s="4">
+        <v>200</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="I25" s="1">
         <v>83</v>
       </c>
@@ -1730,9 +1766,15 @@
       <c r="E26" s="1">
         <v>54</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="3">
+        <v>45885</v>
+      </c>
+      <c r="G26" s="4">
+        <v>200</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
       <c r="I26" s="1">
         <v>84</v>
       </c>
@@ -1762,9 +1804,15 @@
       <c r="E27" s="1">
         <v>55</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="3">
+        <v>45885</v>
+      </c>
+      <c r="G27" s="4">
+        <v>200</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
       <c r="I27" s="1">
         <v>85</v>
       </c>
@@ -1794,9 +1842,15 @@
       <c r="E28" s="1">
         <v>56</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="1"/>
+      <c r="F28" s="3">
+        <v>45894</v>
+      </c>
+      <c r="G28" s="4">
+        <v>200</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
       <c r="I28" s="1">
         <v>86</v>
       </c>
@@ -1826,9 +1880,15 @@
       <c r="E29" s="1">
         <v>57</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="3">
+        <v>45894</v>
+      </c>
+      <c r="G29" s="4">
+        <v>200</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
       <c r="I29" s="1">
         <v>87</v>
       </c>
@@ -1858,9 +1918,15 @@
       <c r="E30" s="1">
         <v>58</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="3">
+        <v>45894</v>
+      </c>
+      <c r="G30" s="4">
+        <v>200</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
       <c r="I30" s="1">
         <v>88</v>
       </c>
@@ -1890,9 +1956,15 @@
       <c r="E31" s="1">
         <v>59</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="3">
+        <v>45894</v>
+      </c>
+      <c r="G31" s="4">
+        <v>200</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1">
         <v>89</v>
       </c>
@@ -1922,9 +1994,15 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="1"/>
+      <c r="F32" s="3">
+        <v>45894</v>
+      </c>
+      <c r="G32" s="4">
+        <v>200</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
       <c r="I32" s="1">
         <v>90</v>
       </c>

--- a/LoanOfficer-A/2023/122 moirangthem naobi.xlsx
+++ b/LoanOfficer-A/2023/122 moirangthem naobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>12600</v>
+        <v>19400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>11400</v>
+        <v>4600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -898,9 +898,15 @@
       <c r="M3" s="1">
         <v>91</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="1"/>
+      <c r="N3" s="3">
+        <v>45928</v>
+      </c>
+      <c r="O3" s="4">
+        <v>200</v>
+      </c>
+      <c r="P3" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -942,9 +948,15 @@
       <c r="M4" s="1">
         <v>92</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="1"/>
+      <c r="N4" s="3">
+        <v>45928</v>
+      </c>
+      <c r="O4" s="4">
+        <v>200</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -986,9 +998,15 @@
       <c r="M5" s="1">
         <v>93</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="1"/>
+      <c r="N5" s="3">
+        <v>45928</v>
+      </c>
+      <c r="O5" s="4">
+        <v>200</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1018,15 +1036,27 @@
       <c r="I6" s="1">
         <v>64</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1"/>
+      <c r="J6" s="3">
+        <v>45901</v>
+      </c>
+      <c r="K6" s="4">
+        <v>200</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
       <c r="M6" s="1">
         <v>94</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="1"/>
+      <c r="N6" s="3">
+        <v>45928</v>
+      </c>
+      <c r="O6" s="4">
+        <v>200</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1056,15 +1086,27 @@
       <c r="I7" s="1">
         <v>65</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1"/>
+      <c r="J7" s="3">
+        <v>45901</v>
+      </c>
+      <c r="K7" s="4">
+        <v>200</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
       <c r="M7" s="1">
         <v>95</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="1"/>
+      <c r="N7" s="3">
+        <v>45928</v>
+      </c>
+      <c r="O7" s="4">
+        <v>200</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1094,15 +1136,27 @@
       <c r="I8" s="1">
         <v>66</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="1"/>
+      <c r="J8" s="3">
+        <v>45901</v>
+      </c>
+      <c r="K8" s="4">
+        <v>200</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
       <c r="M8" s="1">
         <v>96</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="1"/>
+      <c r="N8" s="3">
+        <v>45928</v>
+      </c>
+      <c r="O8" s="4">
+        <v>200</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1132,15 +1186,27 @@
       <c r="I9" s="1">
         <v>67</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="1"/>
+      <c r="J9" s="3">
+        <v>45901</v>
+      </c>
+      <c r="K9" s="4">
+        <v>200</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
       <c r="M9" s="1">
         <v>97</v>
       </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="1"/>
+      <c r="N9" s="3">
+        <v>45928</v>
+      </c>
+      <c r="O9" s="4">
+        <v>200</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1170,9 +1236,15 @@
       <c r="I10" s="1">
         <v>68</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="1"/>
+      <c r="J10" s="3">
+        <v>45901</v>
+      </c>
+      <c r="K10" s="4">
+        <v>200</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
       <c r="M10" s="1">
         <v>98</v>
       </c>
@@ -1208,9 +1280,15 @@
       <c r="I11" s="1">
         <v>69</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="1"/>
+      <c r="J11" s="3">
+        <v>45901</v>
+      </c>
+      <c r="K11" s="4">
+        <v>200</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
       <c r="M11" s="1">
         <v>99</v>
       </c>
@@ -1246,9 +1324,15 @@
       <c r="I12" s="1">
         <v>70</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="1"/>
+      <c r="J12" s="3">
+        <v>45901</v>
+      </c>
+      <c r="K12" s="4">
+        <v>200</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
       <c r="M12" s="1">
         <v>100</v>
       </c>
@@ -1284,9 +1368,15 @@
       <c r="I13" s="1">
         <v>71</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="1"/>
+      <c r="J13" s="3">
+        <v>45910</v>
+      </c>
+      <c r="K13" s="4">
+        <v>200</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
       <c r="M13" s="1">
         <v>101</v>
       </c>
@@ -1322,9 +1412,15 @@
       <c r="I14" s="1">
         <v>72</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="1"/>
+      <c r="J14" s="3">
+        <v>45910</v>
+      </c>
+      <c r="K14" s="4">
+        <v>200</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
       <c r="M14" s="1">
         <v>102</v>
       </c>
@@ -1360,9 +1456,15 @@
       <c r="I15" s="1">
         <v>73</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="1"/>
+      <c r="J15" s="3">
+        <v>45910</v>
+      </c>
+      <c r="K15" s="4">
+        <v>200</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
       <c r="M15" s="1">
         <v>103</v>
       </c>
@@ -1398,9 +1500,15 @@
       <c r="I16" s="1">
         <v>74</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="1"/>
+      <c r="J16" s="3">
+        <v>45910</v>
+      </c>
+      <c r="K16" s="4">
+        <v>200</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
       <c r="M16" s="1">
         <v>104</v>
       </c>
@@ -1436,9 +1544,15 @@
       <c r="I17" s="1">
         <v>75</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="1"/>
+      <c r="J17" s="3">
+        <v>45910</v>
+      </c>
+      <c r="K17" s="4">
+        <v>200</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
       <c r="M17" s="1">
         <v>105</v>
       </c>
@@ -1474,9 +1588,15 @@
       <c r="I18" s="1">
         <v>76</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="1"/>
+      <c r="J18" s="3">
+        <v>45910</v>
+      </c>
+      <c r="K18" s="4">
+        <v>200</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
       <c r="M18" s="1">
         <v>106</v>
       </c>
@@ -1512,9 +1632,15 @@
       <c r="I19" s="1">
         <v>77</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="1"/>
+      <c r="J19" s="3">
+        <v>45910</v>
+      </c>
+      <c r="K19" s="4">
+        <v>200</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
       <c r="M19" s="1">
         <v>107</v>
       </c>
@@ -1550,9 +1676,15 @@
       <c r="I20" s="1">
         <v>78</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="1"/>
+      <c r="J20" s="3">
+        <v>45914</v>
+      </c>
+      <c r="K20" s="4">
+        <v>200</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
       <c r="M20" s="1">
         <v>108</v>
       </c>
@@ -1588,9 +1720,15 @@
       <c r="I21" s="1">
         <v>79</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="1"/>
+      <c r="J21" s="3">
+        <v>45914</v>
+      </c>
+      <c r="K21" s="4">
+        <v>200</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
       <c r="M21" s="1">
         <v>109</v>
       </c>
@@ -1626,9 +1764,15 @@
       <c r="I22" s="1">
         <v>80</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="1"/>
+      <c r="J22" s="3">
+        <v>45914</v>
+      </c>
+      <c r="K22" s="4">
+        <v>200</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
       <c r="M22" s="1">
         <v>110</v>
       </c>
@@ -1664,9 +1808,15 @@
       <c r="I23" s="1">
         <v>81</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="1"/>
+      <c r="J23" s="3">
+        <v>45914</v>
+      </c>
+      <c r="K23" s="4">
+        <v>200</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
       <c r="M23" s="1">
         <v>111</v>
       </c>
@@ -1702,9 +1852,15 @@
       <c r="I24" s="1">
         <v>82</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="1"/>
+      <c r="J24" s="3">
+        <v>45914</v>
+      </c>
+      <c r="K24" s="4">
+        <v>200</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
       <c r="M24" s="1">
         <v>112</v>
       </c>
@@ -1740,9 +1896,15 @@
       <c r="I25" s="1">
         <v>83</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="1"/>
+      <c r="J25" s="3">
+        <v>45921</v>
+      </c>
+      <c r="K25" s="4">
+        <v>200</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
       <c r="M25" s="1">
         <v>113</v>
       </c>
@@ -1778,9 +1940,15 @@
       <c r="I26" s="1">
         <v>84</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="1"/>
+      <c r="J26" s="3">
+        <v>45921</v>
+      </c>
+      <c r="K26" s="4">
+        <v>200</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1</v>
+      </c>
       <c r="M26" s="1">
         <v>114</v>
       </c>
@@ -1816,9 +1984,15 @@
       <c r="I27" s="1">
         <v>85</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="1"/>
+      <c r="J27" s="3">
+        <v>45921</v>
+      </c>
+      <c r="K27" s="4">
+        <v>200</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
       <c r="M27" s="1">
         <v>115</v>
       </c>
@@ -1854,9 +2028,15 @@
       <c r="I28" s="1">
         <v>86</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="1"/>
+      <c r="J28" s="3">
+        <v>45921</v>
+      </c>
+      <c r="K28" s="4">
+        <v>200</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
       <c r="M28" s="1">
         <v>116</v>
       </c>
@@ -1892,9 +2072,15 @@
       <c r="I29" s="1">
         <v>87</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="1"/>
+      <c r="J29" s="3">
+        <v>45921</v>
+      </c>
+      <c r="K29" s="4">
+        <v>200</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
       <c r="M29" s="1">
         <v>117</v>
       </c>
@@ -1930,9 +2116,15 @@
       <c r="I30" s="1">
         <v>88</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="1"/>
+      <c r="J30" s="3">
+        <v>45921</v>
+      </c>
+      <c r="K30" s="4">
+        <v>200</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1</v>
+      </c>
       <c r="M30" s="1">
         <v>118</v>
       </c>
@@ -1968,9 +2160,15 @@
       <c r="I31" s="1">
         <v>89</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="1"/>
+      <c r="J31" s="3">
+        <v>45921</v>
+      </c>
+      <c r="K31" s="4">
+        <v>200</v>
+      </c>
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
       <c r="M31" s="1">
         <v>119</v>
       </c>
@@ -2006,9 +2204,15 @@
       <c r="I32" s="1">
         <v>90</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="1"/>
+      <c r="J32" s="3">
+        <v>45928</v>
+      </c>
+      <c r="K32" s="4">
+        <v>200</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
       <c r="M32" s="1">
         <v>120</v>
       </c>

--- a/LoanOfficer-A/2023/122 moirangthem naobi.xlsx
+++ b/LoanOfficer-A/2023/122 moirangthem naobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>19400</v>
+        <v>22200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>4600</v>
+        <v>1800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1248,9 +1248,15 @@
       <c r="M10" s="1">
         <v>98</v>
       </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="1"/>
+      <c r="N10" s="3">
+        <v>45933</v>
+      </c>
+      <c r="O10" s="4">
+        <v>200</v>
+      </c>
+      <c r="P10" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1292,9 +1298,15 @@
       <c r="M11" s="1">
         <v>99</v>
       </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="1"/>
+      <c r="N11" s="3">
+        <v>45933</v>
+      </c>
+      <c r="O11" s="4">
+        <v>200</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1336,9 +1348,15 @@
       <c r="M12" s="1">
         <v>100</v>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="1"/>
+      <c r="N12" s="3">
+        <v>45933</v>
+      </c>
+      <c r="O12" s="4">
+        <v>200</v>
+      </c>
+      <c r="P12" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1380,9 +1398,15 @@
       <c r="M13" s="1">
         <v>101</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="1"/>
+      <c r="N13" s="3">
+        <v>45933</v>
+      </c>
+      <c r="O13" s="4">
+        <v>200</v>
+      </c>
+      <c r="P13" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1424,9 +1448,15 @@
       <c r="M14" s="1">
         <v>102</v>
       </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="1"/>
+      <c r="N14" s="3">
+        <v>45933</v>
+      </c>
+      <c r="O14" s="4">
+        <v>200</v>
+      </c>
+      <c r="P14" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1468,9 +1498,15 @@
       <c r="M15" s="1">
         <v>103</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="1"/>
+      <c r="N15" s="3">
+        <v>45933</v>
+      </c>
+      <c r="O15" s="4">
+        <v>200</v>
+      </c>
+      <c r="P15" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -1512,9 +1548,15 @@
       <c r="M16" s="1">
         <v>104</v>
       </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="1"/>
+      <c r="N16" s="3">
+        <v>45933</v>
+      </c>
+      <c r="O16" s="4">
+        <v>200</v>
+      </c>
+      <c r="P16" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1556,9 +1598,15 @@
       <c r="M17" s="1">
         <v>105</v>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="1"/>
+      <c r="N17" s="3">
+        <v>45933</v>
+      </c>
+      <c r="O17" s="4">
+        <v>200</v>
+      </c>
+      <c r="P17" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
@@ -1600,9 +1648,15 @@
       <c r="M18" s="1">
         <v>106</v>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="1"/>
+      <c r="N18" s="3">
+        <v>45933</v>
+      </c>
+      <c r="O18" s="4">
+        <v>200</v>
+      </c>
+      <c r="P18" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -1644,9 +1698,15 @@
       <c r="M19" s="1">
         <v>107</v>
       </c>
-      <c r="N19" s="3"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="1"/>
+      <c r="N19" s="3">
+        <v>45933</v>
+      </c>
+      <c r="O19" s="4">
+        <v>200</v>
+      </c>
+      <c r="P19" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -1688,9 +1748,15 @@
       <c r="M20" s="1">
         <v>108</v>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="1"/>
+      <c r="N20" s="3">
+        <v>45933</v>
+      </c>
+      <c r="O20" s="4">
+        <v>200</v>
+      </c>
+      <c r="P20" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
@@ -1732,9 +1798,15 @@
       <c r="M21" s="1">
         <v>109</v>
       </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="1"/>
+      <c r="N21" s="3">
+        <v>45933</v>
+      </c>
+      <c r="O21" s="4">
+        <v>200</v>
+      </c>
+      <c r="P21" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -1776,9 +1848,15 @@
       <c r="M22" s="1">
         <v>110</v>
       </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="1"/>
+      <c r="N22" s="3">
+        <v>45933</v>
+      </c>
+      <c r="O22" s="4">
+        <v>200</v>
+      </c>
+      <c r="P22" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
@@ -1820,9 +1898,15 @@
       <c r="M23" s="1">
         <v>111</v>
       </c>
-      <c r="N23" s="3"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="1"/>
+      <c r="N23" s="3">
+        <v>45933</v>
+      </c>
+      <c r="O23" s="4">
+        <v>200</v>
+      </c>
+      <c r="P23" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">

--- a/LoanOfficer-A/2023/122 moirangthem naobi.xlsx
+++ b/LoanOfficer-A/2023/122 moirangthem naobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>22200</v>
+        <v>22800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1948,9 +1948,15 @@
       <c r="M24" s="1">
         <v>112</v>
       </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="1"/>
+      <c r="N24" s="3">
+        <v>45947</v>
+      </c>
+      <c r="O24" s="4">
+        <v>200</v>
+      </c>
+      <c r="P24" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -1992,9 +1998,15 @@
       <c r="M25" s="1">
         <v>113</v>
       </c>
-      <c r="N25" s="3"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="1"/>
+      <c r="N25" s="3">
+        <v>45947</v>
+      </c>
+      <c r="O25" s="4">
+        <v>200</v>
+      </c>
+      <c r="P25" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -2036,9 +2048,15 @@
       <c r="M26" s="1">
         <v>114</v>
       </c>
-      <c r="N26" s="3"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="1"/>
+      <c r="N26" s="3">
+        <v>45947</v>
+      </c>
+      <c r="O26" s="4">
+        <v>200</v>
+      </c>
+      <c r="P26" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
